--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2022/American_Aircraft_Cumulative_Statistics_2022.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2022/American_Aircraft_Cumulative_Statistics_2022.xlsx
@@ -13,39 +13,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24" uniqueCount="24">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Breeze</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -127,10 +130,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="true"/>
+    <col min="1" max="1" width="9.28515625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -150,40 +153,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -191,40 +194,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>3361327187</v>
+        <v>14938940868</v>
       </c>
       <c r="C2" s="0">
-        <v>3941472300</v>
+        <v>18278059723</v>
       </c>
       <c r="D2" s="0">
-        <v>405085</v>
+        <v>379449</v>
       </c>
       <c r="E2" s="0">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="F2" s="0">
-        <v>27260</v>
+        <v>192093</v>
       </c>
       <c r="G2" s="0">
-        <v>2.7999999999999998</v>
+        <v>3.9900000000000002</v>
       </c>
       <c r="H2" s="0">
-        <v>7.5199999999999996</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="I2" s="0">
-        <v>85.280000000000001</v>
+        <v>81.730000000000004</v>
       </c>
       <c r="J2" s="0">
-        <v>964</v>
+        <v>743</v>
       </c>
       <c r="K2" s="0">
-        <v>6525</v>
+        <v>5032.3400000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>43.5</v>
+        <v>39.32</v>
       </c>
       <c r="M2" s="0">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="3">
@@ -232,40 +235,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>12051625661</v>
+        <v>6182844973</v>
       </c>
       <c r="C3" s="0">
-        <v>14052413586</v>
+        <v>7305467889</v>
       </c>
       <c r="D3" s="0">
-        <v>486243</v>
+        <v>425231</v>
       </c>
       <c r="E3" s="0">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="F3" s="0">
-        <v>82465</v>
+        <v>68635</v>
       </c>
       <c r="G3" s="0">
-        <v>2.8500000000000001</v>
+        <v>4</v>
       </c>
       <c r="H3" s="0">
-        <v>6.9900000000000002</v>
+        <v>8.3300000000000001</v>
       </c>
       <c r="I3" s="0">
-        <v>85.760000000000005</v>
+        <v>84.629999999999995</v>
       </c>
       <c r="J3" s="0">
-        <v>929</v>
+        <v>710</v>
       </c>
       <c r="K3" s="0">
-        <v>5486</v>
+        <v>5581.3100000000004</v>
       </c>
       <c r="L3" s="0">
-        <v>29.920000000000002</v>
+        <v>37.210000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="4">
@@ -273,40 +276,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>6182844973</v>
+        <v>46672012929</v>
       </c>
       <c r="C4" s="0">
-        <v>7305467889</v>
+        <v>53754952783</v>
       </c>
       <c r="D4" s="0">
-        <v>425231</v>
+        <v>676248</v>
       </c>
       <c r="E4" s="0">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="F4" s="0">
-        <v>68635</v>
+        <v>270589</v>
       </c>
       <c r="G4" s="0">
-        <v>4</v>
+        <v>3.3999999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>8.3300000000000001</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I4" s="0">
-        <v>84.629999999999995</v>
+        <v>86.819999999999993</v>
       </c>
       <c r="J4" s="0">
-        <v>710</v>
+        <v>1100</v>
       </c>
       <c r="K4" s="0">
-        <v>5581</v>
+        <v>7032.5</v>
       </c>
       <c r="L4" s="0">
-        <v>37.210000000000001</v>
+        <v>38.710000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.11</v>
+        <v>0.10199999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -314,40 +317,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>5856962</v>
+        <v>17528043437</v>
       </c>
       <c r="C5" s="0">
-        <v>7871718</v>
+        <v>20248687279</v>
       </c>
       <c r="D5" s="0">
-        <v>65535</v>
+        <v>983901</v>
       </c>
       <c r="E5" s="0">
-        <v>129</v>
+        <v>196</v>
       </c>
       <c r="F5" s="0">
-        <v>51</v>
+        <v>56486</v>
       </c>
       <c r="G5" s="0">
-        <v>65535</v>
+        <v>2.7400000000000002</v>
       </c>
       <c r="H5" s="0">
-        <v>65535</v>
+        <v>11.710000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>74.409999999999997</v>
+        <v>86.560000000000002</v>
       </c>
       <c r="J5" s="0">
-        <v>1169</v>
+        <v>1830</v>
       </c>
       <c r="K5" s="0">
-        <v>0</v>
+        <v>7421.4499999999998</v>
       </c>
       <c r="L5" s="0">
-        <v>0</v>
+        <v>37.890000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="6">
@@ -355,40 +358,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>8380034940</v>
+        <v>48741444232</v>
       </c>
       <c r="C6" s="0">
-        <v>9999311482</v>
+        <v>57810875371</v>
       </c>
       <c r="D6" s="0">
-        <v>471443</v>
+        <v>560509</v>
       </c>
       <c r="E6" s="0">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F6" s="0">
-        <v>84251</v>
+        <v>356358</v>
       </c>
       <c r="G6" s="0">
-        <v>3.9700000000000002</v>
+        <v>3.46</v>
       </c>
       <c r="H6" s="0">
-        <v>8.4499999999999993</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="I6" s="0">
-        <v>83.810000000000002</v>
+        <v>84.310000000000002</v>
       </c>
       <c r="J6" s="0">
-        <v>756</v>
+        <v>943</v>
       </c>
       <c r="K6" s="0">
-        <v>6016</v>
+        <v>6226.2799999999997</v>
       </c>
       <c r="L6" s="0">
-        <v>38.329999999999998</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="M6" s="0">
-        <v>0.11</v>
+        <v>0.10000000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -396,40 +399,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>2667834641</v>
+        <v>9339986426</v>
       </c>
       <c r="C7" s="0">
-        <v>3281782104</v>
+        <v>10997311395</v>
       </c>
       <c r="D7" s="0">
-        <v>719689</v>
+        <v>717840</v>
       </c>
       <c r="E7" s="0">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F7" s="0">
-        <v>18443</v>
+        <v>48613</v>
       </c>
       <c r="G7" s="0">
-        <v>4.04</v>
+        <v>3.1699999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>10.890000000000001</v>
+        <v>10.65</v>
       </c>
       <c r="I7" s="0">
-        <v>81.290000000000006</v>
+        <v>84.930000000000007</v>
       </c>
       <c r="J7" s="0">
-        <v>978</v>
+        <v>1315</v>
       </c>
       <c r="K7" s="0">
-        <v>5085</v>
+        <v>6098.1400000000003</v>
       </c>
       <c r="L7" s="0">
-        <v>27.949999999999999</v>
+        <v>35.460000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.089999999999999997</v>
       </c>
     </row>
     <row r="8">
@@ -437,40 +440,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>24059456200</v>
+        <v>9647073000</v>
       </c>
       <c r="C8" s="0">
-        <v>29999087418</v>
+        <v>11923251058</v>
       </c>
       <c r="D8" s="0">
-        <v>632092</v>
+        <v>1251128</v>
       </c>
       <c r="E8" s="0">
-        <v>161</v>
+        <v>233</v>
       </c>
       <c r="F8" s="0">
-        <v>153495</v>
+        <v>14928</v>
       </c>
       <c r="G8" s="0">
-        <v>3.23</v>
+        <v>1.5700000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>10.220000000000001</v>
+        <v>11.029999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>80.200000000000003</v>
+        <v>80.909999999999997</v>
       </c>
       <c r="J8" s="0">
-        <v>1213</v>
+        <v>3437</v>
       </c>
       <c r="K8" s="0">
-        <v>6187</v>
+        <v>11651.82</v>
       </c>
       <c r="L8" s="0">
-        <v>38.399999999999999</v>
+        <v>50.130000000000003</v>
       </c>
       <c r="M8" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -478,40 +481,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>13593989283</v>
+        <v>10281592003</v>
       </c>
       <c r="C9" s="0">
-        <v>16700403364</v>
+        <v>13149779910</v>
       </c>
       <c r="D9" s="0">
-        <v>729913</v>
+        <v>1641670</v>
       </c>
       <c r="E9" s="0">
-        <v>182</v>
+        <v>282</v>
       </c>
       <c r="F9" s="0">
-        <v>91563</v>
+        <v>11469</v>
       </c>
       <c r="G9" s="0">
-        <v>4</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>10.619999999999999</v>
+        <v>11.77</v>
       </c>
       <c r="I9" s="0">
-        <v>81.400000000000006</v>
+        <v>78.189999999999998</v>
       </c>
       <c r="J9" s="0">
-        <v>1002</v>
+        <v>4098</v>
       </c>
       <c r="K9" s="0">
-        <v>4993</v>
+        <v>13764.48</v>
       </c>
       <c r="L9" s="0">
-        <v>27.43</v>
+        <v>49.189999999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.099000000000000005</v>
       </c>
     </row>
     <row r="10">
@@ -519,40 +522,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>13275366076</v>
+        <v>18412322467</v>
       </c>
       <c r="C10" s="0">
-        <v>15757590450</v>
+        <v>23691050932</v>
       </c>
       <c r="D10" s="0">
-        <v>446138</v>
+        <v>1389504</v>
       </c>
       <c r="E10" s="0">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="F10" s="0">
-        <v>113147</v>
+        <v>22270</v>
       </c>
       <c r="G10" s="0">
-        <v>3.2000000000000002</v>
+        <v>1.3100000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>8.1400000000000006</v>
+        <v>10.51</v>
       </c>
       <c r="I10" s="0">
-        <v>84.25</v>
+        <v>77.719999999999999</v>
       </c>
       <c r="J10" s="0">
-        <v>928</v>
+        <v>3914</v>
       </c>
       <c r="K10" s="0">
-        <v>6133</v>
+        <v>14906.08</v>
       </c>
       <c r="L10" s="0">
-        <v>40.890000000000001</v>
+        <v>54.840000000000003</v>
       </c>
       <c r="M10" s="0">
-        <v>0.11</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="11">
@@ -560,40 +563,81 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>83578335923</v>
+        <v>9755205506</v>
       </c>
       <c r="C11" s="0">
-        <v>101045400311</v>
+        <v>12726467614</v>
       </c>
       <c r="D11" s="0">
-        <v>539657</v>
+        <v>1740967</v>
       </c>
       <c r="E11" s="0">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="F11" s="0">
-        <v>639310</v>
+        <v>9530</v>
       </c>
       <c r="G11" s="0">
-        <v>3.4100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="H11" s="0">
-        <v>8.8800000000000008</v>
+        <v>11.720000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>82.709999999999994</v>
+        <v>76.650000000000006</v>
       </c>
       <c r="J11" s="0">
-        <v>964</v>
+        <v>4393</v>
       </c>
       <c r="K11" s="0">
-        <v>5829</v>
+        <v>16854.220000000001</v>
       </c>
       <c r="L11" s="0">
-        <v>35.609999999999999</v>
+        <v>55.450000000000003</v>
       </c>
       <c r="M11" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>191499465841</v>
+      </c>
+      <c r="C12" s="0">
+        <v>229885903954</v>
+      </c>
+      <c r="D12" s="0">
+        <v>705648</v>
+      </c>
+      <c r="E12" s="0">
+        <v>173</v>
+      </c>
+      <c r="F12" s="0">
+        <v>1050971</v>
+      </c>
+      <c r="G12" s="0">
+        <v>3.23</v>
+      </c>
+      <c r="H12" s="0">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="I12" s="0">
+        <v>83.299999999999997</v>
+      </c>
+      <c r="J12" s="0">
+        <v>1161</v>
+      </c>
+      <c r="K12" s="0">
+        <v>7517.8999999999996</v>
+      </c>
+      <c r="L12" s="0">
+        <v>40.869999999999997</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.10299999999999999</v>
       </c>
     </row>
   </sheetData>
